--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125681469</v>
+        <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(F.Weber.) H.Buch</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -729,7 +717,7 @@
         <v>392649</v>
       </c>
       <c r="R2" t="n">
-        <v>6704989</v>
+        <v>6704979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På äldre barrlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125681481</v>
+        <v>125681419</v>
       </c>
       <c r="B3" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,26 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392650</v>
+        <v>392580</v>
       </c>
       <c r="R3" t="n">
-        <v>6704984</v>
+        <v>6705007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125681472</v>
+        <v>125681481</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,25 +905,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -944,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392649</v>
+        <v>392650</v>
       </c>
       <c r="R4" t="n">
-        <v>6704989</v>
+        <v>6704984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125681419</v>
+        <v>125681469</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,26 +1013,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392580</v>
+        <v>392649</v>
       </c>
       <c r="R5" t="n">
-        <v>6705007</v>
+        <v>6704989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,15 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125681494</v>
+        <v>125681472</v>
       </c>
       <c r="B6" t="n">
-        <v>96513</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,27 +1121,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,7 +1151,7 @@
         <v>392649</v>
       </c>
       <c r="R6" t="n">
-        <v>6704979</v>
+        <v>6704989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,11 +1184,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På äldre barrlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96568</v>
+        <v>96575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96575</v>
+        <v>96578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125681419</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125681481</v>
       </c>
       <c r="B4" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>125681469</v>
       </c>
       <c r="B5" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>125681472</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96578</v>
+        <v>96582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125681419</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125681481</v>
       </c>
       <c r="B4" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>125681469</v>
       </c>
       <c r="B5" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>125681472</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96582</v>
+        <v>96583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96583</v>
+        <v>96585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125681419</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125681481</v>
       </c>
       <c r="B4" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>125681469</v>
       </c>
       <c r="B5" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>125681472</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96585</v>
+        <v>96587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96589</v>
+        <v>96593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125681419</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125681481</v>
       </c>
       <c r="B4" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>125681469</v>
       </c>
       <c r="B5" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>125681472</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96593</v>
+        <v>96596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125681494</v>
       </c>
       <c r="B2" t="n">
-        <v>96596</v>
+        <v>97349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125681419</v>
+        <v>125681469</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,26 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392580</v>
+        <v>392649</v>
       </c>
       <c r="R3" t="n">
-        <v>6705007</v>
+        <v>6704989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +892,7 @@
         <v>125681481</v>
       </c>
       <c r="B4" t="n">
-        <v>79009</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125681469</v>
+        <v>125681445</v>
       </c>
       <c r="B5" t="n">
-        <v>79009</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,33 +1008,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1048,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392649</v>
+        <v>392597</v>
       </c>
       <c r="R5" t="n">
-        <v>6704989</v>
+        <v>6705020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,14 +1097,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125681472</v>
+        <v>125681419</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,8 +1125,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>392649</v>
+        <v>392580</v>
       </c>
       <c r="R6" t="n">
-        <v>6704989</v>
+        <v>6705007</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,6 +1181,11 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I gammal gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1207,6 +1207,311 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125681438</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NV Lundbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>392590</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6705013</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i senvuxen gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125681472</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NV Lundbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>392649</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6704989</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125681508</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NV Lundbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>392573</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6705029</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57190-2024 artfynd.xlsx
+++ b/artfynd/A 57190-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681469</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681445</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681419</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681438</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681472</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,8 +1552,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>